--- a/data/azucena/inputs/azu_lib_plus5.xlsx
+++ b/data/azucena/inputs/azu_lib_plus5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\azucena\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888A3134-79FE-4703-BE77-7B8C2C9E9EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1A59C4-2C55-4B78-B08A-6B77CD82977F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25200" yWindow="405" windowWidth="21600" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
+    <workbookView xWindow="5520" yWindow="525" windowWidth="17055" windowHeight="14955" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>B</t>
   </si>
@@ -69,9 +69,6 @@
     <t>DB1</t>
   </si>
   <si>
-    <t>SSL~b</t>
-  </si>
-  <si>
     <t>Power Crush</t>
   </si>
   <si>
@@ -145,6 +142,21 @@
   </si>
   <si>
     <t>LIB.d3</t>
+  </si>
+  <si>
+    <t>SWL</t>
+  </si>
+  <si>
+    <t>df2</t>
+  </si>
+  <si>
+    <t>1+2</t>
+  </si>
+  <si>
+    <t>LIB stand</t>
+  </si>
+  <si>
+    <t>SSL</t>
   </si>
 </sst>
 </file>
@@ -244,11 +256,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -599,10 +610,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -610,7 +621,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -633,8 +644,8 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B9BB04-D3D2-4E07-A007-5B16E4AB0AD8}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
@@ -652,7 +663,7 @@
     <col min="9" max="9" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -669,21 +680,30 @@
         <v>9</v>
       </c>
       <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1">
         <v>4</v>
@@ -698,21 +718,30 @@
         <v>-5</v>
       </c>
       <c r="F2">
+        <v>-83</v>
+      </c>
+      <c r="G2">
+        <v>-58</v>
+      </c>
+      <c r="H2">
+        <v>-9</v>
+      </c>
+      <c r="I2">
+        <v>16</v>
+      </c>
+      <c r="J2">
         <v>-76</v>
       </c>
-      <c r="G2">
-        <v>-6</v>
-      </c>
-      <c r="H2">
+      <c r="K2">
         <v>16</v>
       </c>
-      <c r="I2" s="1">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1">
         <v>-76</v>
@@ -727,21 +756,30 @@
         <v>-5</v>
       </c>
       <c r="F3">
+        <v>-83</v>
+      </c>
+      <c r="G3">
+        <v>-58</v>
+      </c>
+      <c r="H3">
+        <v>-13</v>
+      </c>
+      <c r="I3">
+        <v>36</v>
+      </c>
+      <c r="J3">
         <v>-76</v>
       </c>
-      <c r="G3">
-        <v>-10</v>
-      </c>
-      <c r="H3">
+      <c r="K3">
         <v>36</v>
       </c>
-      <c r="I3" s="1">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -759,18 +797,27 @@
         <v>21</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H4">
+        <v>-2</v>
+      </c>
+      <c r="I4">
         <v>17</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1">
         <v>15</v>
@@ -788,18 +835,27 @@
         <v>15</v>
       </c>
       <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
         <v>18</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>-64</v>
       </c>
-      <c r="I5">
+      <c r="J5" s="2">
         <v>-45</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1">
         <v>-8</v>
@@ -817,18 +873,27 @@
         <v>-8</v>
       </c>
       <c r="G6">
+        <v>-8</v>
+      </c>
+      <c r="H6">
         <v>38</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>-64</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>-45</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>38</v>
+      </c>
+      <c r="L6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -836,31 +901,40 @@
       <c r="C7" s="1">
         <v>14</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>10</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>14</v>
       </c>
       <c r="G7">
-        <v>-6</v>
-      </c>
-      <c r="H7" s="4">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>-9</v>
+      </c>
+      <c r="I7" s="3">
         <v>53</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>70</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1">
-        <v>-76</v>
+        <v>-3.2</v>
       </c>
       <c r="C8" s="1">
         <v>24</v>
@@ -875,21 +949,30 @@
         <v>24</v>
       </c>
       <c r="G8">
-        <v>-10</v>
+        <v>24</v>
       </c>
       <c r="H8">
+        <v>-13</v>
+      </c>
+      <c r="I8">
         <v>56</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>70</v>
+      </c>
+      <c r="L8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
-        <v>-76</v>
+        <v>-37</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -904,18 +987,27 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="H9">
+        <v>-13</v>
+      </c>
+      <c r="I9">
         <v>45</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K9">
+        <v>59</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1">
         <v>-28</v>
@@ -933,18 +1025,27 @@
         <v>35</v>
       </c>
       <c r="G10">
-        <v>-10</v>
+        <v>35</v>
       </c>
       <c r="H10">
+        <v>-13</v>
+      </c>
+      <c r="I10">
         <v>21</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <v>30</v>
+      </c>
+      <c r="L10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -953,30 +1054,39 @@
         <v>-76</v>
       </c>
       <c r="D11">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>43</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H11">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="I11">
+        <v>56</v>
+      </c>
+      <c r="J11">
         <v>-76</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K11">
+        <v>48</v>
+      </c>
+      <c r="L11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="C12">
         <v>83</v>
@@ -991,18 +1101,27 @@
         <v>23</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>53</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>83</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <v>87</v>
+      </c>
+      <c r="L12">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1020,24 +1139,33 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>34.5</v>
       </c>
       <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>34.5</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>34.5</v>
+      </c>
+      <c r="L13">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>32</v>
       </c>
       <c r="C14">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="D14">
         <v>-24</v>
@@ -1049,18 +1177,27 @@
         <v>32</v>
       </c>
       <c r="G14">
+        <v>-68</v>
+      </c>
+      <c r="H14">
         <v>34</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>-64</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>-45</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K14">
+        <v>34</v>
+      </c>
+      <c r="L14">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1078,21 +1215,30 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>40</v>
       </c>
       <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
         <v>-76</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K15">
+        <v>40</v>
+      </c>
+      <c r="L15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>28</v>
@@ -1104,21 +1250,30 @@
         <v>-6</v>
       </c>
       <c r="F16">
-        <v>-76</v>
+        <v>-68</v>
       </c>
       <c r="G16">
-        <v>-2</v>
+        <v>-68</v>
       </c>
       <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
         <v>17</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K16" s="2">
+        <v>-42</v>
+      </c>
+      <c r="L16" s="2">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1136,47 +1291,65 @@
         <v>45</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H17">
-        <v>48</v>
+        <v>-3</v>
       </c>
       <c r="I17">
+        <v>51</v>
+      </c>
+      <c r="J17">
         <v>-76</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>49</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>-40</v>
       </c>
       <c r="E18">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F18">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="G18">
+        <v>-79</v>
+      </c>
+      <c r="H18">
         <v>-16</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>-64</v>
       </c>
-      <c r="I18">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18">
+        <v>80</v>
+      </c>
+      <c r="K18">
+        <v>-42</v>
+      </c>
+      <c r="L18">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1191,27 +1364,36 @@
         <v>-6</v>
       </c>
       <c r="F19">
+        <v>-79</v>
+      </c>
+      <c r="G19">
+        <v>-79</v>
+      </c>
+      <c r="H19">
+        <v>-5</v>
+      </c>
+      <c r="I19">
+        <v>14</v>
+      </c>
+      <c r="J19">
         <v>-76</v>
       </c>
-      <c r="G19">
-        <v>-2</v>
-      </c>
-      <c r="H19">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>7</v>
       </c>
       <c r="C20">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>90</v>
@@ -1220,16 +1402,63 @@
         <v>-6</v>
       </c>
       <c r="F20">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="G20">
+        <v>-79</v>
+      </c>
+      <c r="H20">
         <v>-24</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>-64</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>25</v>
+      </c>
+      <c r="K20">
+        <v>-70</v>
+      </c>
+      <c r="L20">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>72</v>
+      </c>
+      <c r="E21">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>-20</v>
+      </c>
+      <c r="I21">
+        <v>-64</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>67</v>
+      </c>
+      <c r="L21">
+        <v>-25</v>
       </c>
     </row>
   </sheetData>
